--- a/SQExcel.Portal/src/content/docs/ja/docs/images/operation-flow/operation-flow.xlsx
+++ b/SQExcel.Portal/src/content/docs/ja/docs/images/operation-flow/operation-flow.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Repos_MS\East\SQL2Excel\v100\SQL2Excel\SQL2Excel.Help\src\content\docs\ja\images\operation-flow\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Repos_GitEms\sqexcel\SQExcel.Portal\src\content\docs\ja\docs\images\operation-flow\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{806A71E2-70B7-41AC-BEF7-D5F170581395}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7EFE2750-B23A-467B-84F0-4492C34F7718}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="600" yWindow="990" windowWidth="18680" windowHeight="11900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6288" yWindow="3228" windowWidth="19236" windowHeight="12396" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="OPERATION_FLOW" sheetId="2" r:id="rId1"/>
@@ -933,8 +933,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="698500" y="734483"/>
-          <a:ext cx="6146800" cy="4969934"/>
+          <a:off x="694765" y="747930"/>
+          <a:ext cx="6096373" cy="5064063"/>
           <a:chOff x="698500" y="436033"/>
           <a:chExt cx="6146800" cy="4969934"/>
         </a:xfrm>
@@ -3112,270 +3112,6 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>22412</xdr:colOff>
-      <xdr:row>34</xdr:row>
-      <xdr:rowOff>59766</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>37</xdr:col>
-      <xdr:colOff>205292</xdr:colOff>
-      <xdr:row>62</xdr:row>
-      <xdr:rowOff>155014</xdr:rowOff>
-    </xdr:to>
-    <xdr:grpSp>
-      <xdr:nvGrpSpPr>
-        <xdr:cNvPr id="272" name="グループ化 271">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2D592D92-BB29-E5C7-93E1-676987C214B1}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvGrpSpPr/>
-      </xdr:nvGrpSpPr>
-      <xdr:grpSpPr>
-        <a:xfrm>
-          <a:off x="257362" y="7832166"/>
-          <a:ext cx="8641080" cy="6496048"/>
-          <a:chOff x="234950" y="6400801"/>
-          <a:chExt cx="8641080" cy="6496049"/>
-        </a:xfrm>
-      </xdr:grpSpPr>
-      <xdr:pic>
-        <xdr:nvPicPr>
-          <xdr:cNvPr id="266" name="図 265">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F084645B-F7F8-355B-ACB4-FE34BBA3EF29}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvPicPr>
-            <a:picLocks noChangeAspect="1"/>
-          </xdr:cNvPicPr>
-        </xdr:nvPicPr>
-        <xdr:blipFill>
-          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-          <a:stretch>
-            <a:fillRect/>
-          </a:stretch>
-        </xdr:blipFill>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="234950" y="6400801"/>
-            <a:ext cx="8641080" cy="6448303"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-        </xdr:spPr>
-      </xdr:pic>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="267" name="正方形/長方形 266">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D300EC11-B99A-4FFC-A795-B69A92C44BE4}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="5543550" y="12496799"/>
-            <a:ext cx="996950" cy="400051"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:noFill/>
-          <a:ln w="19050">
-            <a:solidFill>
-              <a:srgbClr val="FF0000"/>
-            </a:solidFill>
-          </a:ln>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="2">
-            <a:schemeClr val="accent1">
-              <a:shade val="15000"/>
-            </a:schemeClr>
-          </a:lnRef>
-          <a:fillRef idx="1">
-            <a:schemeClr val="accent1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="lt1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
-            <a:prstTxWarp prst="textNoShape">
-              <a:avLst/>
-            </a:prstTxWarp>
-            <a:noAutofit/>
-          </a:bodyPr>
-          <a:lstStyle/>
-          <a:p>
-            <a:endParaRPr lang="ja-JP" altLang="en-US"/>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="268" name="正方形/長方形 267">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{31FC77C3-38A5-4433-97F9-92EF4DAFAF32}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="3981450" y="7067550"/>
-            <a:ext cx="4362450" cy="1250950"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:noFill/>
-          <a:ln w="19050">
-            <a:solidFill>
-              <a:srgbClr val="FF0000"/>
-            </a:solidFill>
-          </a:ln>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="2">
-            <a:schemeClr val="accent1">
-              <a:shade val="15000"/>
-            </a:schemeClr>
-          </a:lnRef>
-          <a:fillRef idx="1">
-            <a:schemeClr val="accent1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="lt1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
-            <a:prstTxWarp prst="textNoShape">
-              <a:avLst/>
-            </a:prstTxWarp>
-            <a:noAutofit/>
-          </a:bodyPr>
-          <a:lstStyle/>
-          <a:p>
-            <a:endParaRPr lang="ja-JP" altLang="en-US"/>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-      <xdr:cxnSp macro="">
-        <xdr:nvCxnSpPr>
-          <xdr:cNvPr id="269" name="コネクタ: カギ線 268">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{26D16E9E-6245-4675-B883-2BD89611784E}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvCxnSpPr>
-            <a:stCxn id="268" idx="2"/>
-            <a:endCxn id="267" idx="0"/>
-          </xdr:cNvCxnSpPr>
-        </xdr:nvCxnSpPr>
-        <xdr:spPr>
-          <a:xfrm rot="5400000">
-            <a:off x="4013201" y="10347324"/>
-            <a:ext cx="4178299" cy="120650"/>
-          </a:xfrm>
-          <a:prstGeom prst="bentConnector3">
-            <a:avLst>
-              <a:gd name="adj1" fmla="val 50000"/>
-            </a:avLst>
-          </a:prstGeom>
-          <a:ln w="19050">
-            <a:solidFill>
-              <a:srgbClr val="FF0000"/>
-            </a:solidFill>
-            <a:tailEnd type="triangle"/>
-          </a:ln>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="1">
-            <a:schemeClr val="accent1"/>
-          </a:lnRef>
-          <a:fillRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="tx1"/>
-          </a:fontRef>
-        </xdr:style>
-      </xdr:cxnSp>
-    </xdr:grpSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>93</xdr:row>
-      <xdr:rowOff>44824</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>46</xdr:col>
-      <xdr:colOff>228600</xdr:colOff>
-      <xdr:row>127</xdr:row>
-      <xdr:rowOff>117163</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="274" name="図 273">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{59653533-DFFE-290E-3CD0-9ADB95339AA2}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="231588" y="20193000"/>
-          <a:ext cx="10650071" cy="7946339"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>67</xdr:row>
       <xdr:rowOff>67237</xdr:rowOff>
@@ -3399,8 +3135,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="234950" y="15383437"/>
-          <a:ext cx="8641080" cy="5274756"/>
+          <a:off x="233082" y="15683755"/>
+          <a:ext cx="8573845" cy="5377850"/>
           <a:chOff x="234950" y="14240437"/>
           <a:chExt cx="8641080" cy="5274756"/>
         </a:xfrm>
@@ -3419,7 +3155,7 @@
           </xdr:cNvPicPr>
         </xdr:nvPicPr>
         <xdr:blipFill>
-          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
           <a:stretch>
             <a:fillRect/>
           </a:stretch>
@@ -3639,50 +3375,6 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>131</xdr:row>
-      <xdr:rowOff>1</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>46</xdr:col>
-      <xdr:colOff>228600</xdr:colOff>
-      <xdr:row>165</xdr:row>
-      <xdr:rowOff>72340</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="図 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CF8CFDB9-18E7-C157-BCD8-4789EC218672}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="234950" y="28803601"/>
-          <a:ext cx="10801350" cy="7844739"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>22412</xdr:colOff>
       <xdr:row>169</xdr:row>
@@ -3708,7 +3400,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -3717,868 +3409,6 @@
         <a:xfrm>
           <a:off x="485588" y="38070118"/>
           <a:ext cx="2863997" cy="2730640"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>185</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>46</xdr:col>
-      <xdr:colOff>228600</xdr:colOff>
-      <xdr:row>219</xdr:row>
-      <xdr:rowOff>72339</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="5" name="図 4">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4BE1E821-9270-D3BA-9446-0E980F5C4803}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="234950" y="41148000"/>
-          <a:ext cx="10801350" cy="7844739"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>18302</xdr:colOff>
-      <xdr:row>224</xdr:row>
-      <xdr:rowOff>29882</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>47</xdr:col>
-      <xdr:colOff>11952</xdr:colOff>
-      <xdr:row>246</xdr:row>
-      <xdr:rowOff>212517</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="9" name="図 8">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{662EB492-7550-FC6B-30B6-F7335F56F14E}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="249890" y="50747706"/>
-          <a:ext cx="10646709" cy="5277576"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>291</xdr:row>
-      <xdr:rowOff>72571</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>46</xdr:col>
-      <xdr:colOff>228600</xdr:colOff>
-      <xdr:row>326</xdr:row>
-      <xdr:rowOff>226631</xdr:rowOff>
-    </xdr:to>
-    <xdr:grpSp>
-      <xdr:nvGrpSpPr>
-        <xdr:cNvPr id="17" name="グループ化 16">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0CC10EC8-2C13-3CDF-11ED-A3F100978B26}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvGrpSpPr/>
-      </xdr:nvGrpSpPr>
-      <xdr:grpSpPr>
-        <a:xfrm>
-          <a:off x="234950" y="66595171"/>
-          <a:ext cx="10801350" cy="8155060"/>
-          <a:chOff x="217714" y="64949614"/>
-          <a:chExt cx="10800443" cy="8155060"/>
-        </a:xfrm>
-      </xdr:grpSpPr>
-      <xdr:pic>
-        <xdr:nvPicPr>
-          <xdr:cNvPr id="14" name="図 13">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6F9D8040-F2CE-FF4D-162C-0D3DB6AE4E1E}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvPicPr>
-            <a:picLocks noChangeAspect="1"/>
-          </xdr:cNvPicPr>
-        </xdr:nvPicPr>
-        <xdr:blipFill>
-          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
-          <a:stretch>
-            <a:fillRect/>
-          </a:stretch>
-        </xdr:blipFill>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="217714" y="64949614"/>
-            <a:ext cx="10800443" cy="8155060"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-        </xdr:spPr>
-      </xdr:pic>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="15" name="正方形/長方形 14">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{22454733-9F35-4875-80AC-7F372B0BF4CD}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="407307" y="66009157"/>
-            <a:ext cx="2548164" cy="622300"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:noFill/>
-          <a:ln w="19050">
-            <a:solidFill>
-              <a:srgbClr val="FF0000"/>
-            </a:solidFill>
-          </a:ln>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="2">
-            <a:schemeClr val="accent1">
-              <a:shade val="15000"/>
-            </a:schemeClr>
-          </a:lnRef>
-          <a:fillRef idx="1">
-            <a:schemeClr val="accent1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="lt1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
-            <a:prstTxWarp prst="textNoShape">
-              <a:avLst/>
-            </a:prstTxWarp>
-            <a:noAutofit/>
-          </a:bodyPr>
-          <a:lstStyle/>
-          <a:p>
-            <a:endParaRPr lang="ja-JP" altLang="en-US"/>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="16" name="正方形/長方形 15">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A59BA09F-4DC6-40E2-9902-8959088A9A65}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="5015592" y="70270915"/>
-            <a:ext cx="1968413" cy="146499"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:ln/>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="2">
-            <a:schemeClr val="dk1">
-              <a:shade val="15000"/>
-            </a:schemeClr>
-          </a:lnRef>
-          <a:fillRef idx="1">
-            <a:schemeClr val="dk1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="dk1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="lt1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr algn="l"/>
-            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-    </xdr:grpSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>252</xdr:row>
-      <xdr:rowOff>36287</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>46</xdr:col>
-      <xdr:colOff>228600</xdr:colOff>
-      <xdr:row>286</xdr:row>
-      <xdr:rowOff>108625</xdr:rowOff>
-    </xdr:to>
-    <xdr:grpSp>
-      <xdr:nvGrpSpPr>
-        <xdr:cNvPr id="20" name="グループ化 19">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2643E52C-DD36-2CC2-B157-8A5851DAC73A}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvGrpSpPr/>
-      </xdr:nvGrpSpPr>
-      <xdr:grpSpPr>
-        <a:xfrm>
-          <a:off x="234950" y="57643487"/>
-          <a:ext cx="10801350" cy="7844738"/>
-          <a:chOff x="234950" y="56500487"/>
-          <a:chExt cx="10801350" cy="7844738"/>
-        </a:xfrm>
-      </xdr:grpSpPr>
-      <xdr:pic>
-        <xdr:nvPicPr>
-          <xdr:cNvPr id="10" name="図 9">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{759923EC-D991-06A5-94BC-3B50E5DF9FB4}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvPicPr>
-            <a:picLocks noChangeAspect="1"/>
-          </xdr:cNvPicPr>
-        </xdr:nvPicPr>
-        <xdr:blipFill>
-          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9"/>
-          <a:stretch>
-            <a:fillRect/>
-          </a:stretch>
-        </xdr:blipFill>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="234950" y="56500487"/>
-            <a:ext cx="10801350" cy="7844738"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-        </xdr:spPr>
-      </xdr:pic>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="11" name="正方形/長方形 10">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{01E55784-6069-44AC-84A7-FB226EE723E0}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="5031050" y="61611584"/>
-            <a:ext cx="1968413" cy="146499"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:ln/>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="2">
-            <a:schemeClr val="dk1">
-              <a:shade val="15000"/>
-            </a:schemeClr>
-          </a:lnRef>
-          <a:fillRef idx="1">
-            <a:schemeClr val="dk1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="dk1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="lt1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr algn="l"/>
-            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="12" name="正方形/長方形 11">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2D8BB148-F514-4DD2-83E6-053DDEF6D954}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="444917" y="57503895"/>
-            <a:ext cx="1509537" cy="221205"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:noFill/>
-          <a:ln w="19050">
-            <a:solidFill>
-              <a:srgbClr val="FF0000"/>
-            </a:solidFill>
-          </a:ln>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="2">
-            <a:schemeClr val="accent1">
-              <a:shade val="15000"/>
-            </a:schemeClr>
-          </a:lnRef>
-          <a:fillRef idx="1">
-            <a:schemeClr val="accent1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="lt1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
-            <a:prstTxWarp prst="textNoShape">
-              <a:avLst/>
-            </a:prstTxWarp>
-            <a:noAutofit/>
-          </a:bodyPr>
-          <a:lstStyle/>
-          <a:p>
-            <a:endParaRPr lang="ja-JP" altLang="en-US"/>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="18" name="正方形/長方形 17">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DBD12832-D8B3-4714-B3CB-735DBF026D85}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="7283450" y="62919428"/>
-            <a:ext cx="1482272" cy="283029"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:noFill/>
-          <a:ln w="19050">
-            <a:solidFill>
-              <a:srgbClr val="FF0000"/>
-            </a:solidFill>
-          </a:ln>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="2">
-            <a:schemeClr val="accent1">
-              <a:shade val="15000"/>
-            </a:schemeClr>
-          </a:lnRef>
-          <a:fillRef idx="1">
-            <a:schemeClr val="accent1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="lt1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
-            <a:prstTxWarp prst="textNoShape">
-              <a:avLst/>
-            </a:prstTxWarp>
-            <a:noAutofit/>
-          </a:bodyPr>
-          <a:lstStyle/>
-          <a:p>
-            <a:endParaRPr lang="ja-JP" altLang="en-US"/>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="19" name="吹き出し: 四角形 18">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{40129622-85E9-42CA-8223-E7D758C9272C}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="7130143" y="62159242"/>
-            <a:ext cx="2530021" cy="481026"/>
-          </a:xfrm>
-          <a:prstGeom prst="wedgeRectCallout">
-            <a:avLst>
-              <a:gd name="adj1" fmla="val -31436"/>
-              <a:gd name="adj2" fmla="val 119266"/>
-            </a:avLst>
-          </a:prstGeom>
-          <a:ln w="19050">
-            <a:solidFill>
-              <a:srgbClr val="FF0000"/>
-            </a:solidFill>
-          </a:ln>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="2">
-            <a:schemeClr val="accent2"/>
-          </a:lnRef>
-          <a:fillRef idx="1">
-            <a:schemeClr val="lt1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent2"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="dk1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr algn="l"/>
-            <a:r>
-              <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1000">
-                <a:solidFill>
-                  <a:sysClr val="windowText" lastClr="000000"/>
-                </a:solidFill>
-              </a:rPr>
-              <a:t>「既定の接続にする」チェックボックス</a:t>
-            </a:r>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-    </xdr:grpSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>9070</xdr:colOff>
-      <xdr:row>333</xdr:row>
-      <xdr:rowOff>100584</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>47</xdr:col>
-      <xdr:colOff>1813</xdr:colOff>
-      <xdr:row>363</xdr:row>
-      <xdr:rowOff>10131</xdr:rowOff>
-    </xdr:to>
-    <xdr:grpSp>
-      <xdr:nvGrpSpPr>
-        <xdr:cNvPr id="27" name="グループ化 26">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BE13C305-0AC0-FD24-54A4-6A1A1DB11156}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvGrpSpPr/>
-      </xdr:nvGrpSpPr>
-      <xdr:grpSpPr>
-        <a:xfrm>
-          <a:off x="244020" y="76224384"/>
-          <a:ext cx="10800443" cy="6767547"/>
-          <a:chOff x="226785" y="75309984"/>
-          <a:chExt cx="10800443" cy="6767548"/>
-        </a:xfrm>
-      </xdr:grpSpPr>
-      <xdr:pic>
-        <xdr:nvPicPr>
-          <xdr:cNvPr id="21" name="図 20">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FD5E9AB2-D5DF-CE46-4E29-3B42323AA74A}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvPicPr>
-            <a:picLocks noChangeAspect="1"/>
-          </xdr:cNvPicPr>
-        </xdr:nvPicPr>
-        <xdr:blipFill>
-          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId10"/>
-          <a:stretch>
-            <a:fillRect/>
-          </a:stretch>
-        </xdr:blipFill>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="226785" y="75309984"/>
-            <a:ext cx="10800443" cy="6767548"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-        </xdr:spPr>
-      </xdr:pic>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="22" name="正方形/長方形 21">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{603E2938-3EC0-43C3-9FBB-51A82742D6AF}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="226785" y="75839202"/>
-            <a:ext cx="2828275" cy="365421"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:noFill/>
-          <a:ln w="19050">
-            <a:solidFill>
-              <a:srgbClr val="FF0000"/>
-            </a:solidFill>
-          </a:ln>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="2">
-            <a:schemeClr val="accent1">
-              <a:shade val="15000"/>
-            </a:schemeClr>
-          </a:lnRef>
-          <a:fillRef idx="1">
-            <a:schemeClr val="accent1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="lt1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
-            <a:prstTxWarp prst="textNoShape">
-              <a:avLst/>
-            </a:prstTxWarp>
-            <a:noAutofit/>
-          </a:bodyPr>
-          <a:lstStyle/>
-          <a:p>
-            <a:endParaRPr lang="ja-JP" altLang="en-US"/>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="23" name="正方形/長方形 22">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DD5B8984-472F-4F37-8449-BC3B2A9049FA}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="371570" y="81572447"/>
-            <a:ext cx="2828275" cy="284423"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:noFill/>
-          <a:ln w="19050">
-            <a:solidFill>
-              <a:srgbClr val="FF0000"/>
-            </a:solidFill>
-          </a:ln>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="2">
-            <a:schemeClr val="accent1">
-              <a:shade val="15000"/>
-            </a:schemeClr>
-          </a:lnRef>
-          <a:fillRef idx="1">
-            <a:schemeClr val="accent1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="lt1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
-            <a:prstTxWarp prst="textNoShape">
-              <a:avLst/>
-            </a:prstTxWarp>
-            <a:noAutofit/>
-          </a:bodyPr>
-          <a:lstStyle/>
-          <a:p>
-            <a:endParaRPr lang="ja-JP" altLang="en-US"/>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="24" name="正方形/長方形 23">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{349D0308-43C2-4531-8336-6F65DB0F9640}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="3272690" y="75839201"/>
-            <a:ext cx="7707367" cy="5522442"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:noFill/>
-          <a:ln w="19050">
-            <a:solidFill>
-              <a:srgbClr val="FF0000"/>
-            </a:solidFill>
-          </a:ln>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="2">
-            <a:schemeClr val="accent1">
-              <a:shade val="15000"/>
-            </a:schemeClr>
-          </a:lnRef>
-          <a:fillRef idx="1">
-            <a:schemeClr val="accent1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="lt1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
-            <a:prstTxWarp prst="textNoShape">
-              <a:avLst/>
-            </a:prstTxWarp>
-            <a:noAutofit/>
-          </a:bodyPr>
-          <a:lstStyle/>
-          <a:p>
-            <a:endParaRPr lang="ja-JP" altLang="en-US"/>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="25" name="吹き出し: 四角形 24">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AB578EF4-6428-425E-8CA9-0C3E77D2C5BE}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="5810952" y="78473300"/>
-            <a:ext cx="2069397" cy="407059"/>
-          </a:xfrm>
-          <a:prstGeom prst="wedgeRectCallout">
-            <a:avLst>
-              <a:gd name="adj1" fmla="val -20894"/>
-              <a:gd name="adj2" fmla="val 50895"/>
-            </a:avLst>
-          </a:prstGeom>
-          <a:ln w="19050">
-            <a:solidFill>
-              <a:srgbClr val="FF0000"/>
-            </a:solidFill>
-          </a:ln>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="2">
-            <a:schemeClr val="accent2"/>
-          </a:lnRef>
-          <a:fillRef idx="1">
-            <a:schemeClr val="lt1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent2"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="dk1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr algn="ctr"/>
-            <a:r>
-              <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1000">
-                <a:solidFill>
-                  <a:sysClr val="windowText" lastClr="000000"/>
-                </a:solidFill>
-              </a:rPr>
-              <a:t>テーブルグループパネル</a:t>
-            </a:r>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-    </xdr:grpSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>226786</xdr:colOff>
-      <xdr:row>366</xdr:row>
-      <xdr:rowOff>190499</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>34</xdr:col>
-      <xdr:colOff>36214</xdr:colOff>
-      <xdr:row>381</xdr:row>
-      <xdr:rowOff>131569</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="28" name="図 27">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F11A4009-1E8E-3B4D-BC1D-08CAA7167D56}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId11"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="226786" y="82286928"/>
-          <a:ext cx="7828571" cy="3342857"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4613,8 +3443,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="9170519" y="1561355"/>
-          <a:ext cx="6148374" cy="3626003"/>
+          <a:off x="9097681" y="1588249"/>
+          <a:ext cx="6099815" cy="3697721"/>
           <a:chOff x="9170519" y="1561355"/>
           <a:chExt cx="6148374" cy="3626328"/>
         </a:xfrm>
@@ -6044,8 +4874,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="18803470" y="1851211"/>
-          <a:ext cx="4236571" cy="5284694"/>
+          <a:off x="18654058" y="1887070"/>
+          <a:ext cx="4202954" cy="5387788"/>
           <a:chOff x="18810940" y="1513541"/>
           <a:chExt cx="4236571" cy="5284693"/>
         </a:xfrm>
@@ -7325,22 +6155,22 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>7471</xdr:colOff>
-      <xdr:row>421</xdr:row>
-      <xdr:rowOff>97119</xdr:rowOff>
+      <xdr:colOff>22412</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>59766</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>47</xdr:col>
-      <xdr:colOff>4483</xdr:colOff>
-      <xdr:row>449</xdr:row>
-      <xdr:rowOff>205806</xdr:rowOff>
+      <xdr:col>37</xdr:col>
+      <xdr:colOff>205292</xdr:colOff>
+      <xdr:row>62</xdr:row>
+      <xdr:rowOff>155014</xdr:rowOff>
     </xdr:to>
     <xdr:grpSp>
       <xdr:nvGrpSpPr>
-        <xdr:cNvPr id="37" name="グループ化 36">
+        <xdr:cNvPr id="34" name="グループ化 33">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4790C70B-A5BE-2EE1-1BF8-1494D0088730}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9A75C3E4-6897-B1DA-4836-D519EA484C37}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -7348,18 +6178,1580 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="242421" y="96337719"/>
-          <a:ext cx="10804712" cy="6509487"/>
-          <a:chOff x="242421" y="96337719"/>
-          <a:chExt cx="10804712" cy="6509487"/>
+          <a:off x="255494" y="7984566"/>
+          <a:ext cx="8573845" cy="6621554"/>
+          <a:chOff x="258632" y="7832166"/>
+          <a:chExt cx="8686800" cy="6496048"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:grpSp>
+        <xdr:nvGrpSpPr>
+          <xdr:cNvPr id="272" name="グループ化 271">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2D592D92-BB29-E5C7-93E1-676987C214B1}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvGrpSpPr/>
+        </xdr:nvGrpSpPr>
+        <xdr:grpSpPr>
+          <a:xfrm>
+            <a:off x="258632" y="7832166"/>
+            <a:ext cx="8686800" cy="6496048"/>
+            <a:chOff x="234950" y="6400801"/>
+            <a:chExt cx="8641080" cy="6496049"/>
+          </a:xfrm>
+        </xdr:grpSpPr>
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="266" name="図 265">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F084645B-F7F8-355B-ACB4-FE34BBA3EF29}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr>
+              <a:picLocks noChangeAspect="1"/>
+            </xdr:cNvPicPr>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="234950" y="6400801"/>
+              <a:ext cx="8641080" cy="6448303"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="267" name="正方形/長方形 266">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D300EC11-B99A-4FFC-A795-B69A92C44BE4}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="5543550" y="12496799"/>
+              <a:ext cx="996950" cy="400051"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="19050">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent1">
+                <a:shade val="15000"/>
+              </a:schemeClr>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="accent1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="lt1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
+              <a:prstTxWarp prst="textNoShape">
+                <a:avLst/>
+              </a:prstTxWarp>
+              <a:noAutofit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:endParaRPr lang="ja-JP" altLang="en-US"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="268" name="正方形/長方形 267">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{31FC77C3-38A5-4433-97F9-92EF4DAFAF32}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="3981450" y="7067550"/>
+              <a:ext cx="4362450" cy="1250950"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="19050">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent1">
+                <a:shade val="15000"/>
+              </a:schemeClr>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="accent1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="lt1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
+              <a:prstTxWarp prst="textNoShape">
+                <a:avLst/>
+              </a:prstTxWarp>
+              <a:noAutofit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:endParaRPr lang="ja-JP" altLang="en-US"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:cxnSp macro="">
+          <xdr:nvCxnSpPr>
+            <xdr:cNvPr id="269" name="コネクタ: カギ線 268">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{26D16E9E-6245-4675-B883-2BD89611784E}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvCxnSpPr>
+              <a:stCxn id="268" idx="2"/>
+              <a:endCxn id="267" idx="0"/>
+            </xdr:cNvCxnSpPr>
+          </xdr:nvCxnSpPr>
+          <xdr:spPr>
+            <a:xfrm rot="5400000">
+              <a:off x="4013201" y="10347324"/>
+              <a:ext cx="4178299" cy="120650"/>
+            </a:xfrm>
+            <a:prstGeom prst="bentConnector3">
+              <a:avLst>
+                <a:gd name="adj1" fmla="val 50000"/>
+              </a:avLst>
+            </a:prstGeom>
+            <a:ln w="19050">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:tailEnd type="triangle"/>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="1">
+              <a:schemeClr val="accent1"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+        </xdr:cxnSp>
+      </xdr:grpSp>
+      <xdr:pic>
+        <xdr:nvPicPr>
+          <xdr:cNvPr id="32" name="図 31">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{764F02A8-0CAF-46BA-AE60-8ED23D58BCFA}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvPicPr>
+            <a:picLocks noChangeAspect="1"/>
+          </xdr:cNvPicPr>
+        </xdr:nvPicPr>
+        <xdr:blipFill>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+          <a:stretch>
+            <a:fillRect/>
+          </a:stretch>
+        </xdr:blipFill>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="263114" y="7871011"/>
+            <a:ext cx="250352" cy="221456"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+        </xdr:spPr>
+      </xdr:pic>
+    </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>26895</xdr:colOff>
+      <xdr:row>67</xdr:row>
+      <xdr:rowOff>107576</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>41027</xdr:colOff>
+      <xdr:row>68</xdr:row>
+      <xdr:rowOff>100432</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="38" name="図 37">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B9556530-4AA9-4DC2-A521-CC23EA870052}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="259977" y="15724094"/>
+          <a:ext cx="247215" cy="225938"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>93</xdr:row>
+      <xdr:rowOff>44824</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>46</xdr:col>
+      <xdr:colOff>228600</xdr:colOff>
+      <xdr:row>127</xdr:row>
+      <xdr:rowOff>117163</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="41" name="グループ化 40">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{77A720C1-95F2-28AA-B5BF-99F4D4E0133B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="233082" y="21721483"/>
+          <a:ext cx="10717306" cy="7997139"/>
+          <a:chOff x="236220" y="21304624"/>
+          <a:chExt cx="10858500" cy="7844739"/>
         </a:xfrm>
       </xdr:grpSpPr>
       <xdr:pic>
         <xdr:nvPicPr>
-          <xdr:cNvPr id="36" name="図 35">
+          <xdr:cNvPr id="274" name="図 273">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FC650DA4-EE28-153B-C799-C1D39D1EA596}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{59653533-DFFE-290E-3CD0-9ADB95339AA2}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvPicPr>
+            <a:picLocks noChangeAspect="1"/>
+          </xdr:cNvPicPr>
+        </xdr:nvPicPr>
+        <xdr:blipFill>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+          <a:stretch>
+            <a:fillRect/>
+          </a:stretch>
+        </xdr:blipFill>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="236220" y="21304624"/>
+            <a:ext cx="10858500" cy="7844739"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+        </xdr:spPr>
+      </xdr:pic>
+      <xdr:pic>
+        <xdr:nvPicPr>
+          <xdr:cNvPr id="40" name="図 39">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BAC6F775-8F3E-431A-82CD-4C3C2DE43A0D}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvPicPr>
+            <a:picLocks noChangeAspect="1"/>
+          </xdr:cNvPicPr>
+        </xdr:nvPicPr>
+        <xdr:blipFill>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+          <a:stretch>
+            <a:fillRect/>
+          </a:stretch>
+        </xdr:blipFill>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="281044" y="21349447"/>
+            <a:ext cx="250352" cy="221456"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+        </xdr:spPr>
+      </xdr:pic>
+    </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>131</xdr:row>
+      <xdr:rowOff>1</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>46</xdr:col>
+      <xdr:colOff>228600</xdr:colOff>
+      <xdr:row>165</xdr:row>
+      <xdr:rowOff>72340</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="46" name="グループ化 45">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EDB59918-EFAA-B7E0-5DD7-9DE59EEECBC1}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="233082" y="30533789"/>
+          <a:ext cx="10717306" cy="7997139"/>
+          <a:chOff x="236220" y="29946601"/>
+          <a:chExt cx="10858500" cy="7844739"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:pic>
+        <xdr:nvPicPr>
+          <xdr:cNvPr id="2" name="図 1">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CF8CFDB9-18E7-C157-BCD8-4789EC218672}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvPicPr>
+            <a:picLocks noChangeAspect="1"/>
+          </xdr:cNvPicPr>
+        </xdr:nvPicPr>
+        <xdr:blipFill>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+          <a:stretch>
+            <a:fillRect/>
+          </a:stretch>
+        </xdr:blipFill>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="236220" y="29946601"/>
+            <a:ext cx="10858500" cy="7844739"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+        </xdr:spPr>
+      </xdr:pic>
+      <xdr:pic>
+        <xdr:nvPicPr>
+          <xdr:cNvPr id="45" name="図 44">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{436909B9-0D28-4FD7-8621-72779B09511D}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvPicPr>
+            <a:picLocks noChangeAspect="1"/>
+          </xdr:cNvPicPr>
+        </xdr:nvPicPr>
+        <xdr:blipFill>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+          <a:stretch>
+            <a:fillRect/>
+          </a:stretch>
+        </xdr:blipFill>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="279763" y="30001028"/>
+            <a:ext cx="243950" cy="225938"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+        </xdr:spPr>
+      </xdr:pic>
+    </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>185</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>46</xdr:col>
+      <xdr:colOff>228600</xdr:colOff>
+      <xdr:row>219</xdr:row>
+      <xdr:rowOff>72339</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="48" name="グループ化 47">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9E3673F0-BF62-8705-8EF2-92F48D04CF6B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="233082" y="43120235"/>
+          <a:ext cx="10717306" cy="7997139"/>
+          <a:chOff x="236220" y="42291000"/>
+          <a:chExt cx="10858500" cy="7844739"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:pic>
+        <xdr:nvPicPr>
+          <xdr:cNvPr id="5" name="図 4">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4BE1E821-9270-D3BA-9446-0E980F5C4803}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvPicPr>
+            <a:picLocks noChangeAspect="1"/>
+          </xdr:cNvPicPr>
+        </xdr:nvPicPr>
+        <xdr:blipFill>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
+          <a:stretch>
+            <a:fillRect/>
+          </a:stretch>
+        </xdr:blipFill>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="236220" y="42291000"/>
+            <a:ext cx="10858500" cy="7844739"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+        </xdr:spPr>
+      </xdr:pic>
+      <xdr:pic>
+        <xdr:nvPicPr>
+          <xdr:cNvPr id="47" name="図 46">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8A369A3F-01A6-48A9-9D2F-1157433DD15B}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvPicPr>
+            <a:picLocks noChangeAspect="1"/>
+          </xdr:cNvPicPr>
+        </xdr:nvPicPr>
+        <xdr:blipFill>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+          <a:stretch>
+            <a:fillRect/>
+          </a:stretch>
+        </xdr:blipFill>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="281044" y="42353754"/>
+            <a:ext cx="250352" cy="221455"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+        </xdr:spPr>
+      </xdr:pic>
+    </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>18302</xdr:colOff>
+      <xdr:row>224</xdr:row>
+      <xdr:rowOff>29882</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>47</xdr:col>
+      <xdr:colOff>11952</xdr:colOff>
+      <xdr:row>246</xdr:row>
+      <xdr:rowOff>212517</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="51" name="グループ化 50">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F79C4DF5-3D93-829A-555C-488CEE9F8E97}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="251384" y="52240329"/>
+          <a:ext cx="10715439" cy="5310447"/>
+          <a:chOff x="254522" y="51236282"/>
+          <a:chExt cx="10859770" cy="5211835"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:pic>
+        <xdr:nvPicPr>
+          <xdr:cNvPr id="9" name="図 8">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{662EB492-7550-FC6B-30B6-F7335F56F14E}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvPicPr>
+            <a:picLocks noChangeAspect="1"/>
+          </xdr:cNvPicPr>
+        </xdr:nvPicPr>
+        <xdr:blipFill>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
+          <a:stretch>
+            <a:fillRect/>
+          </a:stretch>
+        </xdr:blipFill>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="254522" y="51236282"/>
+            <a:ext cx="10859770" cy="5211835"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+        </xdr:spPr>
+      </xdr:pic>
+      <xdr:pic>
+        <xdr:nvPicPr>
+          <xdr:cNvPr id="50" name="図 49">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D055E2F6-7CE0-4740-A418-25D480C287FB}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvPicPr>
+            <a:picLocks noChangeAspect="1"/>
+          </xdr:cNvPicPr>
+        </xdr:nvPicPr>
+        <xdr:blipFill>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+          <a:stretch>
+            <a:fillRect/>
+          </a:stretch>
+        </xdr:blipFill>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="281044" y="51287083"/>
+            <a:ext cx="250352" cy="221456"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+        </xdr:spPr>
+      </xdr:pic>
+    </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>252</xdr:row>
+      <xdr:rowOff>36287</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>46</xdr:col>
+      <xdr:colOff>228600</xdr:colOff>
+      <xdr:row>286</xdr:row>
+      <xdr:rowOff>108625</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="56" name="グループ化 55">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CBCC21A5-17F8-6094-64E4-11A8AC1FECA9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="233082" y="58773040"/>
+          <a:ext cx="10717306" cy="7997138"/>
+          <a:chOff x="236220" y="57643487"/>
+          <a:chExt cx="10858500" cy="7844738"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:grpSp>
+        <xdr:nvGrpSpPr>
+          <xdr:cNvPr id="20" name="グループ化 19">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2643E52C-DD36-2CC2-B157-8A5851DAC73A}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvGrpSpPr/>
+        </xdr:nvGrpSpPr>
+        <xdr:grpSpPr>
+          <a:xfrm>
+            <a:off x="236220" y="57643487"/>
+            <a:ext cx="10858500" cy="7844738"/>
+            <a:chOff x="234950" y="56500487"/>
+            <a:chExt cx="10801350" cy="7844738"/>
+          </a:xfrm>
+        </xdr:grpSpPr>
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="10" name="図 9">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{759923EC-D991-06A5-94BC-3B50E5DF9FB4}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr>
+              <a:picLocks noChangeAspect="1"/>
+            </xdr:cNvPicPr>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="234950" y="56500487"/>
+              <a:ext cx="10801350" cy="7844738"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="11" name="正方形/長方形 10">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{01E55784-6069-44AC-84A7-FB226EE723E0}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="5031050" y="61611584"/>
+              <a:ext cx="1968413" cy="146499"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:ln/>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="dk1">
+                <a:shade val="15000"/>
+              </a:schemeClr>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="dk1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="dk1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="lt1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="l"/>
+              <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="12" name="正方形/長方形 11">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2D8BB148-F514-4DD2-83E6-053DDEF6D954}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="444917" y="57503895"/>
+              <a:ext cx="1509537" cy="221205"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="19050">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent1">
+                <a:shade val="15000"/>
+              </a:schemeClr>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="accent1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="lt1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
+              <a:prstTxWarp prst="textNoShape">
+                <a:avLst/>
+              </a:prstTxWarp>
+              <a:noAutofit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:endParaRPr lang="ja-JP" altLang="en-US"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="18" name="正方形/長方形 17">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DBD12832-D8B3-4714-B3CB-735DBF026D85}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="7283450" y="62919428"/>
+              <a:ext cx="1482272" cy="283029"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="19050">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent1">
+                <a:shade val="15000"/>
+              </a:schemeClr>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="accent1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="lt1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
+              <a:prstTxWarp prst="textNoShape">
+                <a:avLst/>
+              </a:prstTxWarp>
+              <a:noAutofit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:endParaRPr lang="ja-JP" altLang="en-US"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="19" name="吹き出し: 四角形 18">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{40129622-85E9-42CA-8223-E7D758C9272C}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="7130143" y="62159242"/>
+              <a:ext cx="2530021" cy="481026"/>
+            </a:xfrm>
+            <a:prstGeom prst="wedgeRectCallout">
+              <a:avLst>
+                <a:gd name="adj1" fmla="val -31436"/>
+                <a:gd name="adj2" fmla="val 119266"/>
+              </a:avLst>
+            </a:prstGeom>
+            <a:ln w="19050">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent2"/>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="lt1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent2"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="dk1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="l"/>
+              <a:r>
+                <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1000">
+                  <a:solidFill>
+                    <a:sysClr val="windowText" lastClr="000000"/>
+                  </a:solidFill>
+                </a:rPr>
+                <a:t>「既定の接続にする」チェックボックス</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </xdr:grpSp>
+      <xdr:pic>
+        <xdr:nvPicPr>
+          <xdr:cNvPr id="55" name="図 54">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{416D6E87-4902-4390-AB7C-1004B1CFA199}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvPicPr>
+            <a:picLocks noChangeAspect="1"/>
+          </xdr:cNvPicPr>
+        </xdr:nvPicPr>
+        <xdr:blipFill>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+          <a:stretch>
+            <a:fillRect/>
+          </a:stretch>
+        </xdr:blipFill>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="290008" y="57696847"/>
+            <a:ext cx="250352" cy="221456"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+        </xdr:spPr>
+      </xdr:pic>
+    </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>291</xdr:row>
+      <xdr:rowOff>72571</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>46</xdr:col>
+      <xdr:colOff>228600</xdr:colOff>
+      <xdr:row>326</xdr:row>
+      <xdr:rowOff>226631</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="62" name="グループ化 61">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{52E578E8-30B2-3A72-962C-F1C4C72F2D0C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="233082" y="67899536"/>
+          <a:ext cx="10717306" cy="8311942"/>
+          <a:chOff x="236220" y="66595171"/>
+          <a:chExt cx="10858500" cy="8155060"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:grpSp>
+        <xdr:nvGrpSpPr>
+          <xdr:cNvPr id="17" name="グループ化 16">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0CC10EC8-2C13-3CDF-11ED-A3F100978B26}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvGrpSpPr/>
+        </xdr:nvGrpSpPr>
+        <xdr:grpSpPr>
+          <a:xfrm>
+            <a:off x="236220" y="66595171"/>
+            <a:ext cx="10858500" cy="8155060"/>
+            <a:chOff x="217714" y="64949614"/>
+            <a:chExt cx="10800443" cy="8155060"/>
+          </a:xfrm>
+        </xdr:grpSpPr>
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="14" name="図 13">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6F9D8040-F2CE-FF4D-162C-0D3DB6AE4E1E}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr>
+              <a:picLocks noChangeAspect="1"/>
+            </xdr:cNvPicPr>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId10"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="217714" y="64949614"/>
+              <a:ext cx="10800443" cy="8155060"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="15" name="正方形/長方形 14">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{22454733-9F35-4875-80AC-7F372B0BF4CD}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="407307" y="66009157"/>
+              <a:ext cx="2548164" cy="622300"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="19050">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent1">
+                <a:shade val="15000"/>
+              </a:schemeClr>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="accent1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="lt1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
+              <a:prstTxWarp prst="textNoShape">
+                <a:avLst/>
+              </a:prstTxWarp>
+              <a:noAutofit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:endParaRPr lang="ja-JP" altLang="en-US"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="16" name="正方形/長方形 15">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A59BA09F-4DC6-40E2-9902-8959088A9A65}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="5015592" y="70270915"/>
+              <a:ext cx="1968413" cy="146499"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:ln/>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="dk1">
+                <a:shade val="15000"/>
+              </a:schemeClr>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="dk1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="dk1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="lt1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="l"/>
+              <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </xdr:grpSp>
+      <xdr:pic>
+        <xdr:nvPicPr>
+          <xdr:cNvPr id="61" name="図 60">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C71254BA-4E92-440C-85DE-FE8B184C0EAF}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvPicPr>
+            <a:picLocks noChangeAspect="1"/>
+          </xdr:cNvPicPr>
+        </xdr:nvPicPr>
+        <xdr:blipFill>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+          <a:stretch>
+            <a:fillRect/>
+          </a:stretch>
+        </xdr:blipFill>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="281044" y="66657071"/>
+            <a:ext cx="250352" cy="221456"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+        </xdr:spPr>
+      </xdr:pic>
+    </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>9070</xdr:colOff>
+      <xdr:row>333</xdr:row>
+      <xdr:rowOff>100584</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>47</xdr:col>
+      <xdr:colOff>1813</xdr:colOff>
+      <xdr:row>363</xdr:row>
+      <xdr:rowOff>10131</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="90" name="グループ化 89">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{892A5397-E536-9BE5-369F-D9FB44D03D46}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="242152" y="77717008"/>
+          <a:ext cx="10714532" cy="6902017"/>
+          <a:chOff x="245290" y="76224384"/>
+          <a:chExt cx="10858863" cy="6767547"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:grpSp>
+        <xdr:nvGrpSpPr>
+          <xdr:cNvPr id="27" name="グループ化 26">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BE13C305-0AC0-FD24-54A4-6A1A1DB11156}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvGrpSpPr/>
+        </xdr:nvGrpSpPr>
+        <xdr:grpSpPr>
+          <a:xfrm>
+            <a:off x="245290" y="76224384"/>
+            <a:ext cx="10858863" cy="6767547"/>
+            <a:chOff x="226785" y="75309984"/>
+            <a:chExt cx="10800443" cy="6767548"/>
+          </a:xfrm>
+        </xdr:grpSpPr>
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="21" name="図 20">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FD5E9AB2-D5DF-CE46-4E29-3B42323AA74A}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr>
+              <a:picLocks noChangeAspect="1"/>
+            </xdr:cNvPicPr>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId11"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="226785" y="75309984"/>
+              <a:ext cx="10800443" cy="6767548"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="22" name="正方形/長方形 21">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{603E2938-3EC0-43C3-9FBB-51A82742D6AF}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="226785" y="75839202"/>
+              <a:ext cx="2828275" cy="365421"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="19050">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent1">
+                <a:shade val="15000"/>
+              </a:schemeClr>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="accent1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="lt1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
+              <a:prstTxWarp prst="textNoShape">
+                <a:avLst/>
+              </a:prstTxWarp>
+              <a:noAutofit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:endParaRPr lang="ja-JP" altLang="en-US"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="23" name="正方形/長方形 22">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DD5B8984-472F-4F37-8449-BC3B2A9049FA}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="371570" y="81572447"/>
+              <a:ext cx="2828275" cy="284423"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="19050">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent1">
+                <a:shade val="15000"/>
+              </a:schemeClr>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="accent1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="lt1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
+              <a:prstTxWarp prst="textNoShape">
+                <a:avLst/>
+              </a:prstTxWarp>
+              <a:noAutofit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:endParaRPr lang="ja-JP" altLang="en-US"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="24" name="正方形/長方形 23">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{349D0308-43C2-4531-8336-6F65DB0F9640}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="3272690" y="75839201"/>
+              <a:ext cx="7707367" cy="5522442"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln w="19050">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent1">
+                <a:shade val="15000"/>
+              </a:schemeClr>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="accent1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="lt1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
+              <a:prstTxWarp prst="textNoShape">
+                <a:avLst/>
+              </a:prstTxWarp>
+              <a:noAutofit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:endParaRPr lang="ja-JP" altLang="en-US"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="25" name="吹き出し: 四角形 24">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AB578EF4-6428-425E-8CA9-0C3E77D2C5BE}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="5810952" y="78473300"/>
+              <a:ext cx="2069397" cy="407059"/>
+            </a:xfrm>
+            <a:prstGeom prst="wedgeRectCallout">
+              <a:avLst>
+                <a:gd name="adj1" fmla="val -20894"/>
+                <a:gd name="adj2" fmla="val 50895"/>
+              </a:avLst>
+            </a:prstGeom>
+            <a:ln w="19050">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent2"/>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="lt1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent2"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="dk1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="ctr"/>
+              <a:r>
+                <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1000">
+                  <a:solidFill>
+                    <a:sysClr val="windowText" lastClr="000000"/>
+                  </a:solidFill>
+                </a:rPr>
+                <a:t>テーブルグループパネル</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </xdr:grpSp>
+      <xdr:pic>
+        <xdr:nvPicPr>
+          <xdr:cNvPr id="63" name="図 62">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{93C082C7-72FD-4247-9FB2-26DF4C4CD311}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvPicPr>
+            <a:picLocks noChangeAspect="1"/>
+          </xdr:cNvPicPr>
+        </xdr:nvPicPr>
+        <xdr:blipFill>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+          <a:stretch>
+            <a:fillRect/>
+          </a:stretch>
+        </xdr:blipFill>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="263114" y="76258271"/>
+            <a:ext cx="250352" cy="221456"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+        </xdr:spPr>
+      </xdr:pic>
+    </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>226786</xdr:colOff>
+      <xdr:row>366</xdr:row>
+      <xdr:rowOff>190499</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>34</xdr:col>
+      <xdr:colOff>36214</xdr:colOff>
+      <xdr:row>381</xdr:row>
+      <xdr:rowOff>131569</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="108" name="グループ化 107">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7AB548D9-5C2C-269B-29BD-EC3C3FEEB98E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="226786" y="85498640"/>
+          <a:ext cx="7734228" cy="3437305"/>
+          <a:chOff x="226786" y="83858099"/>
+          <a:chExt cx="7840908" cy="3370070"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:pic>
+        <xdr:nvPicPr>
+          <xdr:cNvPr id="28" name="図 27">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F11A4009-1E8E-3B4D-BC1D-08CAA7167D56}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -7375,69 +7767,43 @@
         </xdr:blipFill>
         <xdr:spPr>
           <a:xfrm>
-            <a:off x="242421" y="96337719"/>
-            <a:ext cx="10804712" cy="6509487"/>
+            <a:off x="226786" y="83858099"/>
+            <a:ext cx="7840908" cy="3370070"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
           </a:prstGeom>
         </xdr:spPr>
       </xdr:pic>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="30" name="正方形/長方形 29">
+      <xdr:pic>
+        <xdr:nvPicPr>
+          <xdr:cNvPr id="95" name="図 94">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6EBD9F0B-CD59-406A-BCE2-CE4ADCC7315C}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{60AEB884-F31E-4BBF-AB15-734398752C04}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
+          <xdr:cNvPicPr>
+            <a:picLocks noChangeAspect="1"/>
+          </xdr:cNvPicPr>
+        </xdr:nvPicPr>
+        <xdr:blipFill>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+          <a:stretch>
+            <a:fillRect/>
+          </a:stretch>
+        </xdr:blipFill>
         <xdr:spPr>
           <a:xfrm>
-            <a:off x="5007802" y="96832941"/>
-            <a:ext cx="3347303" cy="302044"/>
+            <a:off x="281044" y="83914129"/>
+            <a:ext cx="307213" cy="273423"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
           </a:prstGeom>
-          <a:noFill/>
-          <a:ln w="19050">
-            <a:solidFill>
-              <a:srgbClr val="FF0000"/>
-            </a:solidFill>
-          </a:ln>
         </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="2">
-            <a:schemeClr val="accent1">
-              <a:shade val="15000"/>
-            </a:schemeClr>
-          </a:lnRef>
-          <a:fillRef idx="1">
-            <a:schemeClr val="accent1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="lt1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
-            <a:prstTxWarp prst="textNoShape">
-              <a:avLst/>
-            </a:prstTxWarp>
-            <a:noAutofit/>
-          </a:bodyPr>
-          <a:lstStyle/>
-          <a:p>
-            <a:endParaRPr lang="ja-JP" altLang="en-US"/>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
+      </xdr:pic>
     </xdr:grpSp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
@@ -7456,10 +7822,10 @@
     </xdr:to>
     <xdr:grpSp>
       <xdr:nvGrpSpPr>
-        <xdr:cNvPr id="29" name="グループ化 28">
+        <xdr:cNvPr id="111" name="グループ化 110">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E6198EF8-3FFC-5828-A183-A59C2A414525}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3904D017-95EC-01CC-47A3-9B3F8DF4BB14}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -7467,18 +7833,18 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="242422" y="88359130"/>
-          <a:ext cx="10804711" cy="6509488"/>
-          <a:chOff x="242422" y="88359130"/>
-          <a:chExt cx="10804711" cy="6509488"/>
+          <a:off x="240554" y="90089318"/>
+          <a:ext cx="10718800" cy="6634994"/>
+          <a:chOff x="243692" y="88359130"/>
+          <a:chExt cx="10863131" cy="6509488"/>
         </a:xfrm>
       </xdr:grpSpPr>
       <xdr:grpSp>
         <xdr:nvGrpSpPr>
-          <xdr:cNvPr id="35" name="グループ化 34">
+          <xdr:cNvPr id="29" name="グループ化 28">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2B4F8B88-9AFA-3BD9-8199-247D698A0B10}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E6198EF8-3FFC-5828-A183-A59C2A414525}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -7486,18 +7852,122 @@
         </xdr:nvGrpSpPr>
         <xdr:grpSpPr>
           <a:xfrm>
-            <a:off x="242422" y="88359130"/>
-            <a:ext cx="10804711" cy="6509488"/>
+            <a:off x="243692" y="88359130"/>
+            <a:ext cx="10863131" cy="6509488"/>
             <a:chOff x="242422" y="88359130"/>
             <a:chExt cx="10804711" cy="6509488"/>
           </a:xfrm>
         </xdr:grpSpPr>
+        <xdr:grpSp>
+          <xdr:nvGrpSpPr>
+            <xdr:cNvPr id="35" name="グループ化 34">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2B4F8B88-9AFA-3BD9-8199-247D698A0B10}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvGrpSpPr/>
+          </xdr:nvGrpSpPr>
+          <xdr:grpSpPr>
+            <a:xfrm>
+              <a:off x="242422" y="88359130"/>
+              <a:ext cx="10804711" cy="6509488"/>
+              <a:chOff x="242422" y="88359130"/>
+              <a:chExt cx="10804711" cy="6509488"/>
+            </a:xfrm>
+          </xdr:grpSpPr>
+          <xdr:pic>
+            <xdr:nvPicPr>
+              <xdr:cNvPr id="33" name="図 32">
+                <a:extLst>
+                  <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                    <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{822F9F4C-3F76-BF61-31DD-4136275C8ACF}"/>
+                  </a:ext>
+                </a:extLst>
+              </xdr:cNvPr>
+              <xdr:cNvPicPr>
+                <a:picLocks noChangeAspect="1"/>
+              </xdr:cNvPicPr>
+            </xdr:nvPicPr>
+            <xdr:blipFill>
+              <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId13"/>
+              <a:stretch>
+                <a:fillRect/>
+              </a:stretch>
+            </xdr:blipFill>
+            <xdr:spPr>
+              <a:xfrm>
+                <a:off x="242422" y="88359130"/>
+                <a:ext cx="10804711" cy="6509488"/>
+              </a:xfrm>
+              <a:prstGeom prst="rect">
+                <a:avLst/>
+              </a:prstGeom>
+            </xdr:spPr>
+          </xdr:pic>
+          <xdr:sp macro="" textlink="">
+            <xdr:nvSpPr>
+              <xdr:cNvPr id="4" name="正方形/長方形 3">
+                <a:extLst>
+                  <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                    <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2640236C-9081-4437-B3C8-19C69FD23068}"/>
+                  </a:ext>
+                </a:extLst>
+              </xdr:cNvPr>
+              <xdr:cNvSpPr/>
+            </xdr:nvSpPr>
+            <xdr:spPr>
+              <a:xfrm>
+                <a:off x="5015164" y="88854527"/>
+                <a:ext cx="3348177" cy="301174"/>
+              </a:xfrm>
+              <a:prstGeom prst="rect">
+                <a:avLst/>
+              </a:prstGeom>
+              <a:noFill/>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:srgbClr val="FF0000"/>
+                </a:solidFill>
+              </a:ln>
+            </xdr:spPr>
+            <xdr:style>
+              <a:lnRef idx="2">
+                <a:schemeClr val="accent1">
+                  <a:shade val="15000"/>
+                </a:schemeClr>
+              </a:lnRef>
+              <a:fillRef idx="1">
+                <a:schemeClr val="accent1"/>
+              </a:fillRef>
+              <a:effectRef idx="0">
+                <a:schemeClr val="accent1"/>
+              </a:effectRef>
+              <a:fontRef idx="minor">
+                <a:schemeClr val="lt1"/>
+              </a:fontRef>
+            </xdr:style>
+            <xdr:txBody>
+              <a:bodyPr rot="0" spcFirstLastPara="0" vert="horz" wrap="square" lIns="91440" tIns="45720" rIns="91440" bIns="45720" numCol="1" spcCol="0" rtlCol="0" fromWordArt="0" anchor="ctr" anchorCtr="0" forceAA="0" compatLnSpc="1">
+                <a:prstTxWarp prst="textNoShape">
+                  <a:avLst/>
+                </a:prstTxWarp>
+                <a:noAutofit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:endParaRPr lang="ja-JP" altLang="en-US"/>
+              </a:p>
+            </xdr:txBody>
+          </xdr:sp>
+        </xdr:grpSp>
         <xdr:pic>
           <xdr:nvPicPr>
-            <xdr:cNvPr id="33" name="図 32">
+            <xdr:cNvPr id="13" name="図 12">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{822F9F4C-3F76-BF61-31DD-4136275C8ACF}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C34BEC56-161C-8FD7-0753-59A85FA73868}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -7506,15 +7976,128 @@
             </xdr:cNvPicPr>
           </xdr:nvPicPr>
           <xdr:blipFill>
-            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId13"/>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId14"/>
             <a:stretch>
               <a:fillRect/>
             </a:stretch>
           </xdr:blipFill>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="242422" y="88359130"/>
-              <a:ext cx="10804711" cy="6509488"/>
+              <a:off x="7455274" y="89427422"/>
+              <a:ext cx="1017074" cy="1344336"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+      </xdr:grpSp>
+      <xdr:pic>
+        <xdr:nvPicPr>
+          <xdr:cNvPr id="109" name="図 108">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7DCAF73B-0BCC-4F2F-843F-A3DA6888AB41}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvPicPr>
+            <a:picLocks noChangeAspect="1"/>
+          </xdr:cNvPicPr>
+        </xdr:nvPicPr>
+        <xdr:blipFill>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+          <a:stretch>
+            <a:fillRect/>
+          </a:stretch>
+        </xdr:blipFill>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="263114" y="88392001"/>
+            <a:ext cx="250352" cy="221455"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+        </xdr:spPr>
+      </xdr:pic>
+    </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>7471</xdr:colOff>
+      <xdr:row>421</xdr:row>
+      <xdr:rowOff>97119</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>47</xdr:col>
+      <xdr:colOff>4483</xdr:colOff>
+      <xdr:row>449</xdr:row>
+      <xdr:rowOff>205806</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="113" name="グループ化 112">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{720D4A4E-A956-EFB6-22B9-B54E6733E5F3}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="240553" y="98224790"/>
+          <a:ext cx="10718801" cy="6634992"/>
+          <a:chOff x="243691" y="96337719"/>
+          <a:chExt cx="10863132" cy="6509487"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:grpSp>
+        <xdr:nvGrpSpPr>
+          <xdr:cNvPr id="37" name="グループ化 36">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4790C70B-A5BE-2EE1-1BF8-1494D0088730}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvGrpSpPr/>
+        </xdr:nvGrpSpPr>
+        <xdr:grpSpPr>
+          <a:xfrm>
+            <a:off x="243691" y="96337719"/>
+            <a:ext cx="10863132" cy="6509487"/>
+            <a:chOff x="242421" y="96337719"/>
+            <a:chExt cx="10804712" cy="6509487"/>
+          </a:xfrm>
+        </xdr:grpSpPr>
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="36" name="図 35">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FC650DA4-EE28-153B-C799-C1D39D1EA596}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr>
+              <a:picLocks noChangeAspect="1"/>
+            </xdr:cNvPicPr>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId15"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="242421" y="96337719"/>
+              <a:ext cx="10804712" cy="6509487"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -7523,10 +8106,10 @@
         </xdr:pic>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="4" name="正方形/長方形 3">
+            <xdr:cNvPr id="30" name="正方形/長方形 29">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2640236C-9081-4437-B3C8-19C69FD23068}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6EBD9F0B-CD59-406A-BCE2-CE4ADCC7315C}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -7534,8 +8117,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="5015164" y="88854527"/>
-              <a:ext cx="3348177" cy="301174"/>
+              <a:off x="5007802" y="96832941"/>
+              <a:ext cx="3347303" cy="302044"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -7579,10 +8162,10 @@
       </xdr:grpSp>
       <xdr:pic>
         <xdr:nvPicPr>
-          <xdr:cNvPr id="13" name="図 12">
+          <xdr:cNvPr id="112" name="図 111">
             <a:extLst>
               <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C34BEC56-161C-8FD7-0753-59A85FA73868}"/>
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FF066B9F-8303-4D7B-B6BF-78EFD68CC051}"/>
               </a:ext>
             </a:extLst>
           </xdr:cNvPr>
@@ -7591,15 +8174,15 @@
           </xdr:cNvPicPr>
         </xdr:nvPicPr>
         <xdr:blipFill>
-          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId14"/>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
           <a:stretch>
             <a:fillRect/>
           </a:stretch>
         </xdr:blipFill>
         <xdr:spPr>
           <a:xfrm>
-            <a:off x="7455274" y="89427422"/>
-            <a:ext cx="1017074" cy="1344336"/>
+            <a:off x="254150" y="96357141"/>
+            <a:ext cx="250352" cy="221456"/>
           </a:xfrm>
           <a:prstGeom prst="rect">
             <a:avLst/>
@@ -7876,12 +8459,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A29FA320-DA47-41A9-9EA7-7E68689E0E1F}">
   <dimension ref="A1:ED573"/>
-  <sheetFormatPr defaultColWidth="3.08203125" defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultColWidth="3.09765625" defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="16384" width="3.08203125" style="1"/>
+    <col min="1" max="16384" width="3.09765625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:134" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:134" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>38</v>
       </c>
@@ -8279,7 +8862,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="3" spans="1:134" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:134" x14ac:dyDescent="0.45">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
@@ -8299,7 +8882,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="4" spans="1:134" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:134" x14ac:dyDescent="0.45">
       <c r="AN4" s="1" t="s">
         <v>40</v>
       </c>
@@ -8307,7 +8890,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="5" spans="1:134" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:134" x14ac:dyDescent="0.45">
       <c r="AN5" s="1" t="s">
         <v>37</v>
       </c>
@@ -8315,7 +8898,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="6" spans="1:134" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:134" x14ac:dyDescent="0.45">
       <c r="AN6" s="1" t="s">
         <v>41</v>
       </c>
@@ -8323,12 +8906,12 @@
         <v>44</v>
       </c>
     </row>
-    <row r="7" spans="1:134" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:134" x14ac:dyDescent="0.45">
       <c r="CD7" s="1" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A33" s="1" t="s">
         <v>0</v>
       </c>
@@ -8336,15 +8919,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B34" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B42" s="2"/>
     </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="65" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A65" s="1" t="s">
         <v>0</v>
       </c>
@@ -8352,20 +8935,20 @@
         <v>4</v>
       </c>
     </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="66" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B66" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="67" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B67" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="82" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B82" s="2"/>
     </row>
-    <row r="92" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="92" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A92" s="1" t="s">
         <v>0</v>
       </c>
@@ -8373,15 +8956,15 @@
         <v>9</v>
       </c>
     </row>
-    <row r="93" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="93" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B93" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="106" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="106" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B106" s="2"/>
     </row>
-    <row r="130" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="130" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A130" s="1" t="s">
         <v>0</v>
       </c>
@@ -8389,18 +8972,18 @@
         <v>8</v>
       </c>
     </row>
-    <row r="131" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="131" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B131" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="145" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="145" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B145" s="2"/>
     </row>
-    <row r="164" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="164" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B164" s="2"/>
     </row>
-    <row r="168" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="168" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A168" s="1" t="s">
         <v>0</v>
       </c>
@@ -8408,12 +8991,12 @@
         <v>13</v>
       </c>
     </row>
-    <row r="169" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="169" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B169" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="183" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="183" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A183" s="1" t="s">
         <v>0</v>
       </c>
@@ -8421,20 +9004,20 @@
         <v>12</v>
       </c>
     </row>
-    <row r="184" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="184" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B184" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="185" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="185" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B185" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="203" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="203" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B203" s="2"/>
     </row>
-    <row r="222" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="222" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A222" s="1" t="s">
         <v>0</v>
       </c>
@@ -8442,20 +9025,20 @@
         <v>15</v>
       </c>
     </row>
-    <row r="223" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="223" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B223" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="224" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="224" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B224" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="236" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="236" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B236" s="2"/>
     </row>
-    <row r="249" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="249" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A249" s="1" t="s">
         <v>0</v>
       </c>
@@ -8463,28 +9046,28 @@
         <v>18</v>
       </c>
     </row>
-    <row r="250" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="250" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B250" s="1" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="251" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="251" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B251" s="1" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="252" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="252" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B252" s="1" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="258" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="258" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B258" s="2"/>
     </row>
-    <row r="277" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="277" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B277" s="2"/>
     </row>
-    <row r="289" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="289" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A289" s="1" t="s">
         <v>0</v>
       </c>
@@ -8492,20 +9075,20 @@
         <v>21</v>
       </c>
     </row>
-    <row r="290" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="290" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B290" s="1" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="291" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="291" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B291" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="301" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="301" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B301" s="2"/>
     </row>
-    <row r="330" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="330" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A330" s="1" t="s">
         <v>0</v>
       </c>
@@ -8513,25 +9096,25 @@
         <v>25</v>
       </c>
     </row>
-    <row r="331" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="331" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B331" s="1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="332" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="332" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B332" s="1" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="333" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="333" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B333" s="3" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="356" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="356" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B356" s="2"/>
     </row>
-    <row r="365" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="365" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A365" s="1" t="s">
         <v>0</v>
       </c>
@@ -8539,15 +9122,15 @@
         <v>29</v>
       </c>
     </row>
-    <row r="366" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="366" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B366" s="1" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="383" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="383" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B383" s="2"/>
     </row>
-    <row r="384" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="384" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A384" s="1" t="s">
         <v>0</v>
       </c>
@@ -8555,20 +9138,20 @@
         <v>30</v>
       </c>
     </row>
-    <row r="385" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="385" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B385" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="386" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="386" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B386" s="1" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="410" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="410" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B410" s="2"/>
     </row>
-    <row r="419" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="419" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A419" s="1" t="s">
         <v>0</v>
       </c>
@@ -8576,29 +9159,29 @@
         <v>33</v>
       </c>
     </row>
-    <row r="420" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="420" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B420" s="1" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="421" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="421" spans="1:2" x14ac:dyDescent="0.45">
       <c r="B421" s="1" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="436" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="436" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B436" s="2"/>
     </row>
-    <row r="469" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="469" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B469" s="2"/>
     </row>
-    <row r="511" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="511" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B511" s="2"/>
     </row>
-    <row r="538" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="538" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B538" s="2"/>
     </row>
-    <row r="573" spans="2:2" x14ac:dyDescent="0.55000000000000004">
+    <row r="573" spans="2:2" x14ac:dyDescent="0.45">
       <c r="B573" s="2"/>
     </row>
   </sheetData>
